--- a/Result/profitability/3064.xlsx
+++ b/Result/profitability/3064.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.49</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5574999999999999</v>
+        <v>-0.6399999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>84.11125</v>
+        <v>86.10625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.72</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6724999999999999</v>
+        <v>-0.6824999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>82.92750000000001</v>
+        <v>83.10625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.32</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6649999999999999</v>
+        <v>-0.6325</v>
       </c>
       <c r="N4" t="n">
-        <v>80.12875</v>
+        <v>79.81375000000001</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.17</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.55375</v>
+        <v>-0.4687499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>76.8075</v>
+        <v>76.75</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.08</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4012499999999999</v>
+        <v>-0.3737499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>74.02000000000001</v>
+        <v>73.22875000000001</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,13 +1264,13 @@
         <v>-0.31</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3549999999999999</v>
+        <v>-0.2899999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>71.05</v>
+        <v>70.29125000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.27</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1987499999999999</v>
+        <v>-0.2224999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>67.0975</v>
+        <v>66.5975</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>-0.2137499999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>62.955</v>
+        <v>62.95500000000001</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>-0.2587499999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>61.31375000000001</v>
+        <v>61.31375</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3064</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>22</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3</v>
+      </c>
+      <c r="E75" t="n">
+        <v>19</v>
+      </c>
+      <c r="F75" t="n">
+        <v>87.15000000000001</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-16.73%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.5537499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>87.39874999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.04388370817334064</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.6799999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.5964912280701754</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.4599999999999937</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.005250542175550654</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
